--- a/datasets/agenda_implementation/data/output/procedure_status.xlsx
+++ b/datasets/agenda_implementation/data/output/procedure_status.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI0087</t>
+          <t>AI0090</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AI0088</t>
+          <t>AI0091</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI0089</t>
+          <t>AI0092</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AI0090</t>
+          <t>AI0093</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AI0091</t>
+          <t>AI0094</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AI0092</t>
+          <t>AI0095</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI0093</t>
+          <t>AI0096</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AI0094</t>
+          <t>AI0097</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AI0095</t>
+          <t>AI0098</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI0096</t>
+          <t>AI0099</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AI0097</t>
+          <t>AI0100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI0098</t>
+          <t>AI0101</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AI0099</t>
+          <t>AI0102</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AI0100</t>
+          <t>AI0103</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AI0101</t>
+          <t>AI0104</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI0102</t>
+          <t>AI0105</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AI0103</t>
+          <t>AI0106</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI0104</t>
+          <t>AI0107</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AI0105</t>
+          <t>AI0108</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI0106</t>
+          <t>AI0109</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI0107</t>
+          <t>AI0110</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI0108</t>
+          <t>AI0111</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI0109</t>
+          <t>AI0112</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI0110</t>
+          <t>AI0113</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AI0111</t>
+          <t>AI0114</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AI0112</t>
+          <t>AI0115</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI0113</t>
+          <t>AI0116</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI0113</t>
+          <t>AI0116</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AI0114</t>
+          <t>AI0117</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI0115</t>
+          <t>AI0118</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AI0116</t>
+          <t>AI0119</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AI0117</t>
+          <t>AI0120</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AI0118</t>
+          <t>AI0121</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AI0119</t>
+          <t>AI0122</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AI0120</t>
+          <t>AI0123</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AI0121</t>
+          <t>AI0124</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AI0122</t>
+          <t>AI0125</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AI0123</t>
+          <t>AI0126</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
